--- a/mosip_master/xlsx/valid_document.xlsx
+++ b/mosip_master/xlsx/valid_document.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Workspace\SLUDI\MVP\Documents\Master Data\example\sludi-master-data-927\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Workspace\SLUDI\MVP\Training\MaterData\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F9160C-2070-4FAA-933B-E12B3BDA19AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24C7ECF-8028-41EF-B8C5-48A2057E188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3975" windowWidth="28770" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$14</definedName>
+  </definedNames>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
   <si>
     <t>doctyp_code</t>
   </si>
@@ -44,12 +47,6 @@
   </si>
   <si>
     <t>TRUE</t>
-  </si>
-  <si>
-    <t>sin</t>
-  </si>
-  <si>
-    <t>tam</t>
   </si>
   <si>
     <t>PPT</t>
@@ -454,15 +451,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -476,7 +473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -490,35 +487,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -532,40 +529,40 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -574,41 +571,41 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -616,40 +613,40 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -658,371 +655,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="C1:C14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/mosip_master/xlsx/valid_document.xlsx
+++ b/mosip_master/xlsx/valid_document.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Workspace\SLUDI\MVP\Training\MaterData\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\mosip-training\sludi-mvp-dev-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24C7ECF-8028-41EF-B8C5-48A2057E188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFAEB3D-4B0A-498F-9580-BA47FC4F4643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$14</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="23">
   <si>
     <t>doctyp_code</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>SIG</t>
+  </si>
+  <si>
+    <t>Sign</t>
   </si>
 </sst>
 </file>
@@ -646,7 +649,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
